--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260826.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260826.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.09%</t>
+          <t>9.90%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.59%</t>
+          <t>9.85%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.86%</t>
+          <t>8.12%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.80%</t>
+          <t>7.01%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>5,899,000</t>
+          <t>5,979,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.51%</t>
         </is>
       </c>
     </row>
@@ -726,29 +726,29 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.07%</t>
+          <t>5.21%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,486,000</t>
+          <t>2,407,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>4.75%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.70%</t>
         </is>
       </c>
     </row>
@@ -792,29 +792,29 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>4.65%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,407,000</t>
+          <t>2,486,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.43%</t>
+          <t>4.32%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.25%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>3.98%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>89,518,000</t>
+          <t>9,624,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>3.92%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>9,624,000</t>
+          <t>89,518,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.81%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1078,68 +1078,68 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,301,000</t>
+          <t>325,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,424,000</t>
+          <t>1,301,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>255,000</t>
+          <t>2,424,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>4,381,213,268</t>
+          <t>3,227,005,493</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,747,215,338</t>
+          <t>1,879,077,138</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-763,485,754</t>
+          <t>-657,396,740</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>2,121,007,873</t>
+          <t>3,031,007,873</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
